--- a/artfynd/A 33530-2026 artfynd.xlsx
+++ b/artfynd/A 33530-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791499</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791498</v>
       </c>
       <c r="B3" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33530-2026 artfynd.xlsx
+++ b/artfynd/A 33530-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791499</v>
       </c>
       <c r="B2" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791498</v>
       </c>
       <c r="B3" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33530-2026 artfynd.xlsx
+++ b/artfynd/A 33530-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791499</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791498</v>
       </c>
       <c r="B3" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33530-2026 artfynd.xlsx
+++ b/artfynd/A 33530-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791499</v>
       </c>
       <c r="B2" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791498</v>
       </c>
       <c r="B3" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33530-2026 artfynd.xlsx
+++ b/artfynd/A 33530-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791499</v>
       </c>
       <c r="B2" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791498</v>
       </c>
       <c r="B3" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33530-2026 artfynd.xlsx
+++ b/artfynd/A 33530-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791499</v>
       </c>
       <c r="B2" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791498</v>
       </c>
       <c r="B3" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33530-2026 artfynd.xlsx
+++ b/artfynd/A 33530-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791499</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135791498</v>
       </c>
       <c r="B3" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
